--- a/assets/constructions/examples/ctd_tkoi_holder.xlsx
+++ b/assets/constructions/examples/ctd_tkoi_holder.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,11 +584,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CV08-1230</t>
+          <t>V11-1612</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -603,7 +623,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>V08</t>
+          <t>V11</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,16 +634,16 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ISO_5609:12</t>
+          <t>ISO_5609:16</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>VARGUS_V08</t>
+          <t>VARGUS_V11</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -632,18 +652,18 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>11.5</v>
+        <v>15.6</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>90.5</v>
+        <v>80</v>
       </c>
       <c r="P2" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
@@ -679,11 +699,17 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AF2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CVE11-1242</t>
+          <t>CVE08-1221</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -706,7 +732,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>VARGUS_V11</t>
+          <t>VARGUS_V08</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -724,13 +750,13 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>110</v>
+        <v>80.5</v>
       </c>
       <c r="P3" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
@@ -768,62 +794,82 @@
           <t>2021/Groovex Vargus</t>
         </is>
       </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>228.25</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AI3" t="n">
+        <v>20983.87</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CVE08-1221</t>
+          <t>RB18P.0016.03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>HORN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mini-V</t>
+          <t>B18P</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>HORN</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ISO_5609:12</t>
+          <t>ISO_5609:16</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>VARGUS_V08</t>
+          <t>HORN_18P110R</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>80.5</v>
+        <v>130</v>
       </c>
       <c r="P4" t="n">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>56</v>
+      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
@@ -831,7 +877,7 @@
         </is>
       </c>
       <c r="W4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="b">
@@ -845,7 +891,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>HSS</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -854,14 +900,20 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2021/Groovex Vargus</t>
-        </is>
-      </c>
+          <t>2023 / Supermini and mini internal machining</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CV08-1250</t>
+          <t>V16-1622</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -876,7 +928,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>V08</t>
+          <t>V16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -887,16 +939,16 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ISO_5609:12</t>
+          <t>ISO_5609:16</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>VARGUS_V08</t>
+          <t>VARGUS_V16</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -905,18 +957,18 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="P5" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
@@ -952,11 +1004,25 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>150.63</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AI5" t="n">
+        <v>13847.97</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CV14-1264</t>
+          <t>CV14-1234</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -982,7 +1048,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ISO_5609:16</t>
+          <t>ISO_5609:12</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -991,7 +1057,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1000,15 +1066,15 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="P6" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="Q6" t="n">
         <v>11.9</v>
@@ -1048,6 +1114,20 @@
         <is>
           <t>2019 / Groovex Catalog</t>
         </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>328.98</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>30244.35</v>
       </c>
     </row>
   </sheetData>
